--- a/tests/data/testing/phenotype_IND73.xlsx
+++ b/tests/data/testing/phenotype_IND73.xlsx
@@ -444,24 +444,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="33" customWidth="1" min="16" max="16"/>
-    <col width="50" customWidth="1" min="17" max="17"/>
-    <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="23" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -561,108 +561,74 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="180" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HIV.IND.73</t>
+          <t>HIV.IND.EX</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Gonorrhoea test positivity, HIV-positive clients</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>% of people living with HIV who tested positive for gonorrhoea during the reporting period</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>COUNT of clients with "HIV status"='HIV-positive' AND "Gonorrhoea test date" in the reporting period AND "Gonorrhoea test result"='Positive'</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>COUNT of clients with "HIV status"='HIV-positive' AND "Gonorrhoea test date" in the reporting period</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Number of people living with HIV tested for gonorrhoea (using a molecular test, culture or POC test) while attending HIV care and treatment services during the reporting period</t>
-        </is>
+          <t>Example Indicator</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Gender
-Age
-Key population member type
-Type of specimen
-Neisseria gonorrhoeae test type</t>
+Age</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>• Gender (male, female, other*)
-• Age (15–19, 20–24, 25–29, 30–49, 50+ years)
-• Key populations (men who have sex with men, people living in prisons and other closed settings, people who inject drugs, sex workers, trans and gender diverse people)**
-• Diagnostic test used and anatomic site sampled
-• Cities and other administrative regions of epidemiologic importance</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Number of people living with HIV who tested positive for gonorrhoea during the reporting period</t>
-        </is>
+          <t>* Age
+* Gender</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>STI.5B</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Gonorrhoea test date
-Gonorrhoea test result
-HIV status</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>* The category of other includes trans and gender diverse people who choose an identity other than male or female.
-** Where feasible and data security and confidentiality can be ensured (see monitoring considerations in section 3.8 of WHO's HIV SI Guidelines on key populations for further guidance and section 6.4 on maintaining data privacy, security and confidentiality).</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated guidelines on person-centred HIV strategic information: strengthening routine data for impact. Geneva: World Health Organization; 2022</t>
-        </is>
-      </c>
+          <t>EX.1</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Sexually transmitted infections</t>
+          <t>HIV prevention</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>A: % of people attending HIV prevention services who were tested for gonorrhoea and
-had a positive test result during the reporting period
-B: % of people living with HIV who were tested for gonorrhoea and had a positive test result during the reporting period</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>• Gonorrhoea test positivity can be used to highlight areas within a country that require additional support and provide early warning of potential changes in HIV and sexually transmitted infection transmission in the general population.
-• Gonorrhoea test positivity is important information for generating national, regional and global incidence and prevalence estimates for gonorrhoea.
-• Data on gonorrhoea test positivity are important for understanding the challenges imposed by increasing resistance to currently recommended treatment options.</t>
+          <t>Example</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Individual-level data obtained from programme records.  
-If individual-level data are not available, the indicator can be reported using aggregate programme data.</t>
+          <t>Example</t>
         </is>
       </c>
     </row>
